--- a/config/yunying/levelfund.xlsx
+++ b/config/yunying/levelfund.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="levelfund" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="levelfund" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Lv.15に到達</t>
+          <t>达到Lv.15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lv.20に到達</t>
+          <t>达到Lv.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Lv.25に到達</t>
+          <t>达到Lv.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lv.30に到達</t>
+          <t>达到Lv.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lv.35に到達</t>
+          <t>Lv.35等级</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lv.40に到達</t>
+          <t>达到Lv.40</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lv.45に到達</t>
+          <t>达到Lv.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Lv.50に到達</t>
+          <t>达到Lv.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lv.55に到達</t>
+          <t>Lv.55等级</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Lv.60に到達</t>
+          <t>达到Lv.60</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Lv.70に到達</t>
+          <t>达到Lv.70</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Lv.80に到達</t>
+          <t>达到Lv.80</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lv.90に到達</t>
+          <t>达到Lv.90</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
